--- a/translation/review/000scriptAKYO_0010A.xlsx
+++ b/translation/review/000scriptAKYO_0010A.xlsx
@@ -46,7 +46,7 @@
     <t>This girl that kicks her brother in the back of the head right after entering the room is...</t>
   </si>
   <si>
-    <t>Esta chica que patea a su hermano en la parte trasera de la cabeza justo después de entrar al cuarto es...</t>
+    <t>Esta chica que patea a su hermano en la parte＿trasera de la cabeza justo después de entrar al＿cuarto es...</t>
   </si>
   <si>
     <t>Kousaka Kirino : my little sister.</t>
@@ -73,7 +73,7 @@
     <t>W-Why have they gathered in your room to play God Eater?!</t>
   </si>
   <si>
-    <t>¡P-Por qué se han reunido en tu cuarto para jugar God Eater?!</t>
+    <t>¡P-Por qué se han reunido en tu cuarto para＿jugar God Eater?!</t>
   </si>
   <si>
     <t>Saori</t>
@@ -82,7 +82,7 @@
     <t>Pray pardon for the intrusion, Kiririn-shi! What's with the sudden appearance?</t>
   </si>
   <si>
-    <t>¡Perdón por la intrusión, Kiririn-shi! ¿A qué se debe tu repentina aparición?</t>
+    <t>¡Perdón por la intrusión, Kiririn-shi! ¿A qué se＿debe tu repentina aparición?</t>
   </si>
   <si>
     <t>This is Saori Bajeena (online handle name).</t>
@@ -94,13 +94,13 @@
     <t>With her fashion sense and style of speech, she's a typical otaku over 180cm tall.</t>
   </si>
   <si>
-    <t>Con su sentido de la moda y su forma de hablar, es una otaku típica de más de 180cm.</t>
+    <t>Con su sentido de la moda y su forma de hablar,＿es una otaku típica de más de 180cm.</t>
   </si>
   <si>
     <t>Good at helping people, she is the leader of the anime community "Otaku Girls Unite!" that Kirino joined.</t>
   </si>
   <si>
-    <t>Buena para ayudar a la gente, es la líder de la comunidad de anime «Otaku Girls Unite!» a la que se unió Kirino.</t>
+    <t>Buena para ayudar a la gente, es la líder de la＿comunidad de anime «Otaku Girls Unite!» a la＿que se unió Kirino.</t>
   </si>
   <si>
     <t>And now, she is a good friend of mine.</t>
@@ -112,7 +112,7 @@
     <t>On a side note, "Kiririn" is Kirino's handle name.</t>
   </si>
   <si>
-    <t>Por cierto, «Kiririn» es el nombre de usuario de Kirino.</t>
+    <t>Por cierto, «Kiririn» es el nombre de usuario de＿Kirino.</t>
   </si>
   <si>
     <t>Kuroneko</t>
@@ -127,7 +127,7 @@
     <t>Wasn't it you who invited us to play "God Eater Burst"?</t>
   </si>
   <si>
-    <t>¿No fuiste tú quien nos invitó a jugar «God Eater Burst»?</t>
+    <t>¿No fuiste tú quien nos invitó a jugar «God＿Eater Burst»?</t>
   </si>
   <si>
     <t>This is Kuroneko (online handle name).</t>
@@ -139,7 +139,7 @@
     <t>At first glance, she's expressionless and unsociable. A troublesome girl with a sharp tongue.</t>
   </si>
   <si>
-    <t>A primera vista, es inexpresiva y poco sociable. Una chica problemática con una lengua afilada.</t>
+    <t>A primera vista, es inexpresiva y poco sociable.＿Una chica problemática con una lengua afilada.</t>
   </si>
   <si>
     <t>But in reality, she's a very kind hearted person...</t>
@@ -151,31 +151,31 @@
     <t>On a side note, she was recently admitted into my school, becoming my junior in the process.</t>
   </si>
   <si>
-    <t>Por cierto, fue admitida recientemente en mi escuela, convirtiéndose en mi kouhai.</t>
+    <t>Por cierto, fue admitida recientemente en mi＿escuela, convirtiéndose en mi kouhai.</t>
   </si>
   <si>
     <t>She also belongs to the same club as me, but that's kind of a secret between us...</t>
   </si>
   <si>
-    <t>También pertenece al mismo club que yo, pero eso es una especie de secreto entre nosotros...</t>
+    <t>También pertenece al mismo club que yo, pero＿eso es una especie de secreto entre nosotros...</t>
   </si>
   <si>
     <t>She's a worrisome junior to me, a girl I kinda care about... I guess.</t>
   </si>
   <si>
-    <t>Es una kouhai preocupante para mí, una chica por la que me importa... supongo.</t>
+    <t>Es una kouhai preocupante para mí, una chica por＿la que me importa... supongo.</t>
   </si>
   <si>
     <t>That's not it! I'm asking why you are all gathered in his room!</t>
   </si>
   <si>
-    <t>¡Eso no es! ¡Pregunto por qué están todos reunidos en su cuarto!</t>
+    <t>¡Eso no es! ¡Pregunto por qué están todos＿reunidos en su cuarto!</t>
   </si>
   <si>
     <t>Wasn't my room just fine? That's what we did until now!</t>
   </si>
   <si>
-    <t>¿No estaba bien mi cuarto? ¡Eso es lo que hacíamos hasta ahora!</t>
+    <t>¿No estaba bien mi cuarto? ¡Eso es lo que＿hacíamos hasta ahora!</t>
   </si>
   <si>
     <t>Ah, that.</t>
@@ -187,7 +187,7 @@
     <t>Heh. ...It is because we have been gathering in his room a lot recently, so we mistakenly came here.</t>
   </si>
   <si>
-    <t>Je. ...Es porque últimamente nos hemos estado reuniendo mucho en su cuarto, así que vinimos aquí por error.</t>
+    <t>Je. ...Es porque últimamente nos hemos estado＿reuniendo mucho en su cuarto, así que vinimos＿aquí por error.</t>
   </si>
   <si>
     <t>......!!!</t>
@@ -214,7 +214,7 @@
     <t>What's with you? Did you bring your sister's friends into your room when I wasn't around?</t>
   </si>
   <si>
-    <t>¿Qué te pasa? ¿Trajiste a las amigas de tu hermana a tu cuarto cuando no estaba?</t>
+    <t>¿Qué te pasa? ¿Trajiste a las amigas de tu＿hermana a tu cuarto cuando no estaba?</t>
   </si>
   <si>
     <t>Don't make me look like a villain!</t>
@@ -238,37 +238,37 @@
     <t>For some reason, Kirino hasn't been home for three months between winter and spring.</t>
   </si>
   <si>
-    <t>Por alguna razón, Kirino no estuvo en casa durante tres meses entre invierno y primavera.</t>
+    <t>Por alguna razón, Kirino no estuvo en casa＿durante tres meses entre invierno y primavera.</t>
   </si>
   <si>
     <t>She returned home just recently, and that's why she doesn't know what's happened during her absence.</t>
   </si>
   <si>
-    <t>Regresó a casa hace poco, y por eso no sabe lo que ha pasado durante su ausencia.</t>
+    <t>Regresó a casa hace poco, y por eso no sabe lo＿que ha pasado durante su ausencia.</t>
   </si>
   <si>
     <t>It's just that when Kirino wasn't at home, Saori and Kuroneko became "my friends" and used to come over to play.</t>
   </si>
   <si>
-    <t>Es solo que cuando Kirino no estaba en casa, Saori y Kuroneko se volvieron «mis amigas» y solían venir a jugar.</t>
+    <t>Es solo que cuando Kirino no estaba en casa,＿Saori y Kuroneko se volvieron «mis amigas» y＿solían venir a jugar.</t>
   </si>
   <si>
     <t>There's obviously no way what Kirino was suspecting would happen.</t>
   </si>
   <si>
-    <t>Obviamente no hay manera de que ocurriera lo que Kirino sospechaba.</t>
+    <t>Obviamente no hay manera de que ocurriera lo＿que Kirino sospechaba.</t>
   </si>
   <si>
     <t>Although her attitude seems vicious, Kirino just really likes her friends.</t>
   </si>
   <si>
-    <t>Aunque su actitud parece cruel, a Kirino de verdad le agradan sus amigas.</t>
+    <t>Aunque su actitud parece cruel, a Kirino de verdad＿le agradan sus amigas.</t>
   </si>
   <si>
     <t>That's why she was mortified when it looked like I took her friends from her.</t>
   </si>
   <si>
-    <t>Por eso se sintió mortificada cuando parecía que le había quitado a sus amigas.</t>
+    <t>Por eso se sintió mortificada cuando parecía que＿le había quitado a sus amigas.</t>
   </si>
   <si>
     <t>......Hehe...</t>
@@ -283,19 +283,19 @@
     <t>...Even though you asked what was the meaning of this... Right?</t>
   </si>
   <si>
-    <t>...Aunque preguntaste qué significaba esto... ¿Cierto?</t>
+    <t>...Aunque preguntaste qué significaba esto...＿¿Cierto?</t>
   </si>
   <si>
     <t>Hehe... Hey, Kyou-chan? How are we going to explain our relationship to Kirino-chan?</t>
   </si>
   <si>
-    <t>Jeje... Oye, ¿Kyou-chan? ¿Cómo vamos a explicarle nuestra relación a Kirino-chan?</t>
+    <t>Jeje... Oye, ¿Kyou-chan? ¿Cómo vamos a＿explicarle nuestra relación a Kirino-chan?</t>
   </si>
   <si>
     <t>Don't say that as if there's a particular relationship between us!</t>
   </si>
   <si>
-    <t>¡No digas eso como si hubiera una relación especial entre nosotros!</t>
+    <t>¡No digas eso como si hubiera una relación＿especial entre nosotros!</t>
   </si>
   <si>
     <t>Kyou-chan, huh... Disgusting...</t>
@@ -307,7 +307,7 @@
     <t>Oh my, Kirino-chan is angry now... What should we do, Kyou-chan?</t>
   </si>
   <si>
-    <t>Oh, cielos, Kirino-chan está enojada ahora... ¿Qué haremos, Kyou-chan?</t>
+    <t>Oh, cielos, Kirino-chan está enojada ahora...＿¿Qué haremos, Kyou-chan?</t>
   </si>
   <si>
     <t>P-Please just leave it at that...</t>
@@ -328,7 +328,7 @@
     <t>Is that not because he can see Kuroneko-shi's panties from his position?</t>
   </si>
   <si>
-    <t>¿No será porque puede ver las bragas de Kuroneko-shi desde su posición?</t>
+    <t>¿No será porque puede ver las bragas de＿Kuroneko-shi desde su posición?</t>
   </si>
   <si>
     <t>?!</t>
@@ -355,13 +355,13 @@
     <t>Crap! I've just been misunderstood by Kirino, and now...</t>
   </si>
   <si>
-    <t>¡Mierda! Me acaban de malentender Kirino, y ahora...</t>
+    <t>¡Mierda! Me acaban de malentender Kirino, y＿ahora...</t>
   </si>
   <si>
     <t>Y-You're the worst! The worst, the worst, the worst! Just die already!</t>
   </si>
   <si>
-    <t>¡E-Eres lo peor! ¡Lo peor, lo peor, lo peor! ¡Solo muérete ya!</t>
+    <t>¡E-Eres lo peor! ¡Lo peor, lo peor, lo peor! ¡Solo＿muérete ya!</t>
   </si>
   <si>
     <t>...It completely destroyed the mood.</t>
